--- a/database/seeders/xlsx/dastan24.02.xlsx
+++ b/database/seeders/xlsx/dastan24.02.xlsx
@@ -1659,7 +1659,9 @@
       <c r="M2" s="5">
         <v>999999</v>
       </c>
-      <c r="N2" s="13"/>
+      <c r="N2" s="13">
+        <v>0</v>
+      </c>
       <c r="O2" s="5">
         <v>999999</v>
       </c>
@@ -1698,7 +1700,9 @@
       <c r="M3" s="5">
         <v>999999</v>
       </c>
-      <c r="N3" s="13"/>
+      <c r="N3" s="13">
+        <v>0</v>
+      </c>
       <c r="O3" s="5">
         <v>999999</v>
       </c>
@@ -1737,7 +1741,9 @@
       <c r="M4" s="5">
         <v>999999</v>
       </c>
-      <c r="N4" s="13"/>
+      <c r="N4" s="13">
+        <v>0</v>
+      </c>
       <c r="O4" s="5">
         <v>999999</v>
       </c>
@@ -1774,7 +1780,9 @@
       <c r="M5" s="5">
         <v>999999</v>
       </c>
-      <c r="N5" s="13"/>
+      <c r="N5" s="13">
+        <v>0</v>
+      </c>
       <c r="O5" s="5">
         <v>999999</v>
       </c>
@@ -1813,7 +1821,9 @@
       <c r="M6" s="5">
         <v>999999</v>
       </c>
-      <c r="N6" s="13"/>
+      <c r="N6" s="13">
+        <v>0</v>
+      </c>
       <c r="O6" s="5">
         <v>999999</v>
       </c>
@@ -1852,7 +1862,9 @@
       <c r="M7" s="5">
         <v>999999</v>
       </c>
-      <c r="N7" s="5"/>
+      <c r="N7" s="13">
+        <v>0</v>
+      </c>
       <c r="O7" s="5">
         <v>999999</v>
       </c>
@@ -1891,7 +1903,9 @@
       <c r="M8" s="5">
         <v>999999</v>
       </c>
-      <c r="N8" s="5"/>
+      <c r="N8" s="13">
+        <v>0</v>
+      </c>
       <c r="O8" s="5">
         <v>999999</v>
       </c>
@@ -1930,7 +1944,9 @@
       <c r="M9" s="5">
         <v>999999</v>
       </c>
-      <c r="N9" s="5"/>
+      <c r="N9" s="13">
+        <v>0</v>
+      </c>
       <c r="O9" s="5">
         <v>999999</v>
       </c>
@@ -1969,7 +1985,9 @@
       <c r="M10" s="5">
         <v>999999</v>
       </c>
-      <c r="N10" s="5"/>
+      <c r="N10" s="13">
+        <v>0</v>
+      </c>
       <c r="O10" s="5">
         <v>999999</v>
       </c>
@@ -2008,7 +2026,9 @@
       <c r="M11" s="5">
         <v>999999</v>
       </c>
-      <c r="N11" s="13"/>
+      <c r="N11" s="13">
+        <v>0</v>
+      </c>
       <c r="O11" s="5">
         <v>999999</v>
       </c>
@@ -2047,7 +2067,9 @@
       <c r="M12" s="5">
         <v>999999</v>
       </c>
-      <c r="N12" s="13"/>
+      <c r="N12" s="13">
+        <v>0</v>
+      </c>
       <c r="O12" s="5">
         <v>999999</v>
       </c>
@@ -2086,7 +2108,9 @@
       <c r="M13" s="5">
         <v>999999</v>
       </c>
-      <c r="N13" s="13"/>
+      <c r="N13" s="13">
+        <v>0</v>
+      </c>
       <c r="O13" s="5">
         <v>999999</v>
       </c>
@@ -2125,7 +2149,9 @@
       <c r="M14" s="5">
         <v>999999</v>
       </c>
-      <c r="N14" s="13"/>
+      <c r="N14" s="13">
+        <v>0</v>
+      </c>
       <c r="O14" s="5">
         <v>999999</v>
       </c>
@@ -2164,7 +2190,9 @@
       <c r="M15" s="5">
         <v>999999</v>
       </c>
-      <c r="N15" s="5"/>
+      <c r="N15" s="13">
+        <v>0</v>
+      </c>
       <c r="O15" s="5">
         <v>999999</v>
       </c>
@@ -2203,7 +2231,9 @@
       <c r="M16" s="5">
         <v>999999</v>
       </c>
-      <c r="N16" s="5"/>
+      <c r="N16" s="13">
+        <v>0</v>
+      </c>
       <c r="O16" s="5">
         <v>999999</v>
       </c>
@@ -2242,7 +2272,9 @@
       <c r="M17" s="5">
         <v>999999</v>
       </c>
-      <c r="N17" s="13"/>
+      <c r="N17" s="13">
+        <v>0</v>
+      </c>
       <c r="O17" s="5">
         <v>999999</v>
       </c>
@@ -2281,7 +2313,9 @@
       <c r="M18" s="5">
         <v>999999</v>
       </c>
-      <c r="N18" s="13"/>
+      <c r="N18" s="13">
+        <v>0</v>
+      </c>
       <c r="O18" s="5">
         <v>999999</v>
       </c>
@@ -2320,7 +2354,9 @@
       <c r="M19" s="5">
         <v>999999</v>
       </c>
-      <c r="N19" s="13"/>
+      <c r="N19" s="13">
+        <v>0</v>
+      </c>
       <c r="O19" s="5">
         <v>999999</v>
       </c>
@@ -2359,7 +2395,9 @@
       <c r="M20" s="5">
         <v>999999</v>
       </c>
-      <c r="N20" s="13"/>
+      <c r="N20" s="13">
+        <v>0</v>
+      </c>
       <c r="O20" s="5">
         <v>999999</v>
       </c>
@@ -2398,7 +2436,9 @@
       <c r="M21" s="5">
         <v>999999</v>
       </c>
-      <c r="N21" s="13"/>
+      <c r="N21" s="13">
+        <v>0</v>
+      </c>
       <c r="O21" s="5">
         <v>999999</v>
       </c>
@@ -2437,7 +2477,9 @@
       <c r="M22" s="5">
         <v>999999</v>
       </c>
-      <c r="N22" s="13"/>
+      <c r="N22" s="13">
+        <v>0</v>
+      </c>
       <c r="O22" s="5">
         <v>999999</v>
       </c>
@@ -2476,7 +2518,9 @@
       <c r="M23" s="5">
         <v>999999</v>
       </c>
-      <c r="N23" s="13"/>
+      <c r="N23" s="13">
+        <v>0</v>
+      </c>
       <c r="O23" s="5">
         <v>999999</v>
       </c>
@@ -2515,7 +2559,9 @@
       <c r="M24" s="5">
         <v>999999</v>
       </c>
-      <c r="N24" s="13"/>
+      <c r="N24" s="13">
+        <v>0</v>
+      </c>
       <c r="O24" s="5">
         <v>999999</v>
       </c>
@@ -2554,7 +2600,9 @@
       <c r="M25" s="5">
         <v>999999</v>
       </c>
-      <c r="N25" s="13"/>
+      <c r="N25" s="13">
+        <v>0</v>
+      </c>
       <c r="O25" s="5">
         <v>999999</v>
       </c>
@@ -2593,7 +2641,9 @@
       <c r="M26" s="5">
         <v>999999</v>
       </c>
-      <c r="N26" s="5"/>
+      <c r="N26" s="13">
+        <v>0</v>
+      </c>
       <c r="O26" s="5">
         <v>999999</v>
       </c>
@@ -2632,7 +2682,9 @@
       <c r="M27" s="5">
         <v>999999</v>
       </c>
-      <c r="N27" s="5"/>
+      <c r="N27" s="13">
+        <v>0</v>
+      </c>
       <c r="O27" s="5">
         <v>999999</v>
       </c>
@@ -2671,7 +2723,9 @@
       <c r="M28" s="5">
         <v>999999</v>
       </c>
-      <c r="N28" s="5"/>
+      <c r="N28" s="13">
+        <v>0</v>
+      </c>
       <c r="O28" s="5">
         <v>999999</v>
       </c>
@@ -2710,7 +2764,9 @@
       <c r="M29" s="5">
         <v>999999</v>
       </c>
-      <c r="N29" s="5"/>
+      <c r="N29" s="13">
+        <v>0</v>
+      </c>
       <c r="O29" s="5">
         <v>999999</v>
       </c>
@@ -2749,7 +2805,9 @@
       <c r="M30" s="5">
         <v>999999</v>
       </c>
-      <c r="N30" s="5"/>
+      <c r="N30" s="13">
+        <v>0</v>
+      </c>
       <c r="O30" s="5">
         <v>999999</v>
       </c>
@@ -2788,7 +2846,9 @@
       <c r="M31" s="5">
         <v>999999</v>
       </c>
-      <c r="N31" s="5"/>
+      <c r="N31" s="13">
+        <v>0</v>
+      </c>
       <c r="O31" s="5">
         <v>999999</v>
       </c>
@@ -2827,7 +2887,9 @@
       <c r="M32" s="5">
         <v>999999</v>
       </c>
-      <c r="N32" s="5"/>
+      <c r="N32" s="13">
+        <v>0</v>
+      </c>
       <c r="O32" s="5">
         <v>999999</v>
       </c>
@@ -2866,7 +2928,9 @@
       <c r="M33" s="5">
         <v>999999</v>
       </c>
-      <c r="N33" s="5"/>
+      <c r="N33" s="13">
+        <v>0</v>
+      </c>
       <c r="O33" s="5">
         <v>999999</v>
       </c>

--- a/database/seeders/xlsx/dastan24.02.xlsx
+++ b/database/seeders/xlsx/dastan24.02.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="134">
   <si>
     <t>subcategory_id</t>
   </si>
@@ -264,18 +264,6 @@
   </si>
   <si>
     <t>Жұмсақ формуласы бар классикалық балалар сабыны. Жиі қолдануға жарамды, теріні құрғатпайды.</t>
-  </si>
-  <si>
-    <t>Clear Men Балғындық Энергиясы 180мл Мужской шампунь с освежающим эффектом. Удаляет излишки жира, глубоко очищает кожу головы и надолго сохраняет ощущение свежести. Clear Men Балқарағай Ағашы мен Эвкалипт 380мл Мужской шампунь с экстрактами кедрового дерева и эвкалипта. Освежает, ухаживает за кожей головы и укрепляет волосы, придавая им силу и энергию. Чистая Линия Зығыр мен Бидай Сығындысы 400мл Шампунь с натуральными экстрактами льна и пшеницы. Глубоко питает волосы, укрепляет их структуру, придаёт мягкость и естественный блеск. Pro Series Терең Қалпына Келтіру 500мл Профессиональный шампунь для глубокого восстановления повреждённых волос. Укрепляет структуру, делает волосы гладкими и здоровыми. Wash &amp; Go Күш пен Балғындық 360мл Ежедневный шампунь для силы и свежести волос. Глубоко очищает, придаёт лёгкость и поддерживает ощущение чистоты на весь день. Sowell Бальзам Толық Қалпына Келтіру 500мл Бальзам для полного восстановления волос. Увлажняет, питает, придаёт гладкость и мягкость даже сухим и повреждённым волосам. Men's Series Ego 3в1 430мл Мужское средство 3в1: шампунь, гель для душа и кондиционер. Освежает, питает волосы и кожу, обеспечивая комплексный уход. Head &amp; Shoulders 2в1 Негізгі Күтім 400мл Шампунь и кондиционер 2в1 против перхоти. Глубоко очищает кожу головы, предотвращает появление перхоти и делает волосы мягкими. Pantene Тазарту және Қоректендіру 400мл Шампунь для глубокого очищения и питания волос. Натуральные компоненты ухаживают за волосами, придавая им мягкость и блеск. Herbal Essences Терең Қоректендіру Кокос Хош Иісі 350мл Шампунь с глубоким питанием и ароматом кокоса. Увлажняет волосы, делает их гладкими, мягкими и блестящими. Pantene Ылғалдандыру және Қалпына Келтіру 400мл Шампунь для увлажнения и восстановления сухих и повреждённых волос. Глубоко питает, придаёт силу и защищает волосы от повреждений. Pro Series Ұзақ Уақытқа Көлем 500мл Шампунь для придания длительного объёма. Укрепляет волосы, делая их густыми и воздушными. Kerasys Терең Ылғалдандыру 400мл Профессиональный шампунь для интенсивного увлажнения. Делает сухие волосы мягкими, гладкими и здоровыми. Kerasys Ылғалдандырушы Кондиционер 400мл Увлажняющий кондиционер для волос. Восстанавливает естественный баланс влаги, питает и защищает волосы от сухости. Wash &amp; Go Шампунь Ғажайып Жылтырлық пен Қорғау 180мл Шампунь для невероятного блеска и защиты. Глубоко очищает, придаёт волосам гладкость и сохраняет их здоровый вид надолго.</t>
-  </si>
-  <si>
-    <t>Clear Men Балғындық Энергиясы 180мл</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Мужской шампунь с освежающим эффектом. Удаляет излишки жира, глубоко очищает кожу головы и надолго сохраняет ощущение свежести.  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ерлерге арналған сергітетін әсері бар сусабын. Майлы жылтырды кетіреді, бас терісін терең тазартады және ұзақ уақыт балғындық сезімін сақтайды.  </t>
   </si>
   <si>
     <t>Clear men кедровое дерево и эвкалипт 380мл</t>
@@ -1564,12 +1552,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="5.77777777777778" customWidth="1"/>
     <col min="3" max="3" width="14.7777777777778" customWidth="1"/>
-    <col min="4" max="5" width="8.77777777777778" style="1" customWidth="1"/>
+    <col min="4" max="4" width="255.777777777778" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.77777777777778" style="1" customWidth="1"/>
     <col min="6" max="6" width="88.6666666666667" customWidth="1"/>
     <col min="7" max="7" width="158.111111111111" customWidth="1"/>
     <col min="8" max="14" width="8.77777777777778" customWidth="1"/>
@@ -2332,13 +2321,13 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="6" t="s">
         <v>78</v>
       </c>
       <c r="E19" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="20" t="s">
         <v>80</v>
       </c>
       <c r="G19" s="19" t="s">
@@ -2423,7 +2412,7 @@
       <c r="F21" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="8" t="s">
         <v>89</v>
       </c>
       <c r="H21" s="8" t="s">
@@ -2587,7 +2576,7 @@
       <c r="F25" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="5" t="s">
         <v>105</v>
       </c>
       <c r="H25" s="8" t="s">
@@ -2901,45 +2890,23 @@
       </c>
     </row>
     <row r="33" spans="1:17">
-      <c r="A33" s="12">
-        <v>40</v>
-      </c>
+      <c r="A33" s="12"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>20</v>
-      </c>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
-      <c r="M33" s="5">
-        <v>999999</v>
-      </c>
-      <c r="N33" s="13">
-        <v>0</v>
-      </c>
-      <c r="O33" s="5">
-        <v>999999</v>
-      </c>
-      <c r="P33" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q33" s="5">
-        <v>1</v>
-      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="12"/>
@@ -2947,7 +2914,7 @@
       <c r="C34" s="5"/>
       <c r="D34" s="11"/>
       <c r="E34" s="11"/>
-      <c r="F34" s="21"/>
+      <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
@@ -2980,42 +2947,23 @@
       <c r="Q35" s="5"/>
     </row>
     <row r="36" spans="1:17">
-      <c r="A36" s="12"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-    </row>
-    <row r="37" spans="1:17">
-      <c r="A37" s="22"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="23"/>
-      <c r="J37" s="23"/>
-      <c r="K37" s="23"/>
-      <c r="L37" s="23"/>
-      <c r="M37" s="23"/>
-      <c r="N37" s="23"/>
-      <c r="O37" s="23"/>
-      <c r="P37" s="23"/>
-      <c r="Q37" s="23"/>
+      <c r="A36" s="22"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="23"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="23"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="23"/>
+      <c r="Q36" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/database/seeders/xlsx/dastan24.02.xlsx
+++ b/database/seeders/xlsx/dastan24.02.xlsx
@@ -444,7 +444,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -476,12 +476,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF555555"/>
-      <name val="Verdana"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1050,137 +1044,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1223,12 +1217,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1552,7 +1540,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q36"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="5.77777777777778" customWidth="1"/>
@@ -1610,13 +1598,13 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="25" t="s">
+      <c r="O1" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="25" t="s">
+      <c r="P1" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="27" t="s">
+      <c r="Q1" s="23" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1803,10 +1791,10 @@
       <c r="H6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
       <c r="M6" s="5">
         <v>999999</v>
       </c>
@@ -2008,10 +1996,10 @@
       <c r="H11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
       <c r="M11" s="5">
         <v>999999</v>
       </c>
@@ -2049,10 +2037,10 @@
       <c r="H12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
       <c r="M12" s="5">
         <v>999999</v>
       </c>
@@ -2090,10 +2078,10 @@
       <c r="H13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
       <c r="M13" s="5">
         <v>999999</v>
       </c>
@@ -2131,10 +2119,10 @@
       <c r="H14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
       <c r="M14" s="5">
         <v>999999</v>
       </c>
@@ -2888,82 +2876,6 @@
       <c r="Q32" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:17">
-      <c r="A33" s="12"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-    </row>
-    <row r="34" spans="1:17">
-      <c r="A34" s="12"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-    </row>
-    <row r="35" spans="1:17">
-      <c r="A35" s="12"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-    </row>
-    <row r="36" spans="1:17">
-      <c r="A36" s="22"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="23"/>
-      <c r="J36" s="23"/>
-      <c r="K36" s="23"/>
-      <c r="L36" s="23"/>
-      <c r="M36" s="23"/>
-      <c r="N36" s="23"/>
-      <c r="O36" s="23"/>
-      <c r="P36" s="23"/>
-      <c r="Q36" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
